--- a/02-cascade-civic-rev5-ato/artifacts/sctm_control_matrix.xlsx
+++ b/02-cascade-civic-rev5-ato/artifacts/sctm_control_matrix.xlsx
@@ -627,7 +627,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="35.05" customHeight="1" s="16">
+    <row r="5" ht="95" customHeight="1" s="16">
       <c r="A5" s="20" t="inlineStr">
         <is>
           <t>AC-2</t>
@@ -650,7 +650,7 @@
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Partially Implemented</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -660,20 +660,24 @@
       </c>
       <c r="G5" s="20" t="inlineStr">
         <is>
-          <t>Accounts provisioned via Okta tied to HRIS events; privileged accounts require manager + system owner approval; automated disable at 35 days inactivity.</t>
+          <t>Okta/HRIS lifecycle automation and account approvals exist, but four batch jobs share one elevated database account. Process attribution and least privilege are not met for that account; see V-008 / SAR FIND-002.</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>Examine, Interview</t>
+          <t>Examine, Interview, Test</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
         <is>
-          <t>Satisfied</t>
-        </is>
-      </c>
-      <c r="J5" s="20" t="n"/>
+          <t>Other Than Satisfied</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>V-008</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="35.05" customHeight="1" s="16">
       <c r="A6" s="20" t="inlineStr">
